--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="D3">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H3">
         <v>426</v>
